--- a/validationSet.xlsx
+++ b/validationSet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Weather_DBMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7402330F-B262-4139-B9B0-A7A11A13F887}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45BAB0F-2864-4276-981F-767B6D07EA29}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{1F3A2363-7ACB-4494-9CBF-71A47C7776D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="55">
   <si>
     <t>date</t>
   </si>
@@ -117,28 +117,86 @@
     <t>AIWS 20240207.docx</t>
   </si>
   <si>
-    <t>westcentral and adjoining southwest Arabian sea</t>
-  </si>
-  <si>
-    <r>
-      <t>Depression</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+    <t>well marked low pressure with cycir</t>
+  </si>
+  <si>
+    <t>south bay of bengal</t>
+  </si>
+  <si>
+    <t>Long. 66°E to the north of Lat. 32°N</t>
+  </si>
+  <si>
+    <t>AIWS 20221119.docx</t>
+  </si>
+  <si>
+    <t>tROUGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telangana to interior Tamil Nadu ran from Marathwada to north interior Tamil Nadu across interior Karnataka </t>
+  </si>
+  <si>
+    <t>roughly along Long.70°E and to the north of Lat.32°N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">over west Rajasthan and adjoining central Pakistan </t>
+  </si>
+  <si>
+    <t>along Long.89°E to the north of Lat.20°N</t>
+  </si>
+  <si>
+    <t>1.5, 3.1</t>
+  </si>
+  <si>
+    <t>southeast Madhya Pradesh and neighbourhood</t>
+  </si>
+  <si>
+    <t>AIWS 20220403.docx</t>
+  </si>
+  <si>
+    <t>1.5-3.1</t>
+  </si>
+  <si>
+    <t>over Punjab and neighbourhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long.75°E to the north of Lat.32°N. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">over Jharkhand and neighbourhood </t>
+  </si>
+  <si>
+    <t xml:space="preserve">over Punjab TO Jharkhand </t>
+  </si>
+  <si>
+    <t xml:space="preserve">over north interior Karnataka and neighbourhood </t>
+  </si>
+  <si>
+    <t>AIWS 20220124</t>
+  </si>
+  <si>
+    <t>roughly along 70°E to the north of 25°N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south Haryana and neighbourhood lay over Punjab and adjoining Haryana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">over north Tamil Nadu and neighbourhood lay over Kerala and neighbourhood </t>
+  </si>
+  <si>
+    <t xml:space="preserve">over north Andaman sea and neighbourhood </t>
+  </si>
+  <si>
+    <t xml:space="preserve">over north Tamil Nadu and neighbourhood to northeast RajasthaN TO over Kerala and neighbourhood to southwest Madhya Pradesh across interior Karnataka, Marathwada and Vidarbha </t>
+  </si>
+  <si>
+    <t>AIWS 20221011</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,14 +217,24 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri "/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
@@ -192,13 +260,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,8 +583,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988C0674-BBB2-4E71-B697-A00185295065}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
@@ -522,7 +592,7 @@
     <col min="5" max="5" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,7 +609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="1">
         <v>44686</v>
       </c>
@@ -556,7 +626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="1">
         <v>44686</v>
       </c>
@@ -573,7 +643,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="1">
         <v>44686</v>
       </c>
@@ -590,7 +660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>44686</v>
       </c>
@@ -607,7 +677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>44686</v>
       </c>
@@ -624,7 +694,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>44686</v>
       </c>
@@ -641,7 +711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>44686</v>
       </c>
@@ -658,7 +728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>45383</v>
       </c>
@@ -675,7 +745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>45383</v>
       </c>
@@ -692,7 +762,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="1">
         <v>45383</v>
       </c>
@@ -709,7 +779,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="1">
         <v>45383</v>
       </c>
@@ -726,7 +796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="1">
         <v>45329</v>
       </c>
@@ -743,7 +813,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="1">
         <v>45329</v>
       </c>
@@ -760,7 +830,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="16.5">
       <c r="A15" s="1">
         <v>45329</v>
       </c>
@@ -777,7 +847,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="16.5">
       <c r="A16" s="1">
         <v>45329</v>
       </c>
@@ -794,12 +864,293 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="4" t="s">
+    <row r="17" spans="1:5">
+      <c r="A17" s="1">
+        <v>44884</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>7.6</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>30</v>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="1">
+        <v>44884</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>5.8</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1">
+        <v>44654</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19">
+        <v>0.9</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1">
+        <v>44654</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>5.8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1">
+        <v>44654</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21">
+        <v>1.5</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
+        <v>44654</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1">
+        <v>44654</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23">
+        <v>1.5</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
+        <v>44585</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1">
+        <v>44585</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25">
+        <v>5.8</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
+        <v>44585</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>1.5</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
+        <v>44585</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27">
+        <v>1.5</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
+        <v>44585</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>1.5</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16.5">
+      <c r="A29" s="1">
+        <v>44845</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>5.8</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16.5">
+      <c r="A30" s="1">
+        <v>44845</v>
+      </c>
+      <c r="B30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>3.1</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16.5">
+      <c r="A31" s="1">
+        <v>44845</v>
+      </c>
+      <c r="B31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31">
+        <v>1.5</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16.5">
+      <c r="A32" s="1">
+        <v>44845</v>
+      </c>
+      <c r="B32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <v>3.1</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16.5">
+      <c r="A33" s="1">
+        <v>44845</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33">
+        <v>1.5</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
